--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_376_R38.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_376_R38.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.4945</v>
+        <v>7.5212</v>
       </c>
       <c r="E2" t="n">
-        <v>7.8838</v>
+        <v>8.473599999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.3893</v>
+        <v>-0.9524</v>
       </c>
       <c r="G2" t="n">
         <v>5.9532</v>
@@ -610,13 +610,13 @@
         <v>1.6237</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.639</v>
+        <v>-0.6124000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7468</v>
+        <v>-0.1571</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.8922</v>
+        <v>-0.4553</v>
       </c>
       <c r="V2" t="n">
         <v>0.7886</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.0569</v>
+        <v>4.5578</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7291</v>
+        <v>2.4317</v>
       </c>
       <c r="F3" t="n">
-        <v>2.3278</v>
+        <v>2.1261</v>
       </c>
       <c r="G3" t="n">
         <v>4.1168</v>
@@ -688,13 +688,13 @@
         <v>1.6237</v>
       </c>
       <c r="S3" t="n">
-        <v>1.8705</v>
+        <v>0.3714</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5375</v>
+        <v>0.2401</v>
       </c>
       <c r="U3" t="n">
-        <v>0.333</v>
+        <v>0.1314</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3943</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. HERNANGOMEZ</t>
+          <t>K. SLOUKAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.0988</v>
+        <v>4.4265</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.3734</v>
+        <v>1.7584</v>
       </c>
       <c r="F4" t="n">
-        <v>4.4722</v>
+        <v>2.6681</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4251</v>
+        <v>2.6309</v>
       </c>
       <c r="H4" t="n">
-        <v>0.742</v>
+        <v>3.27</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6831</v>
+        <v>-0.6391</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2988</v>
+        <v>1.8801</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9747</v>
+        <v>2.2015</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-0.3213</v>
       </c>
       <c r="M4" t="n">
-        <v>2.1263</v>
+        <v>0.7507</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2327</v>
+        <v>1.0685</v>
       </c>
       <c r="O4" t="n">
-        <v>2.359</v>
+        <v>-0.3178</v>
       </c>
       <c r="P4" t="n">
-        <v>1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0501</v>
+        <v>0.6359</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6721</v>
+        <v>0.1103</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7222</v>
+        <v>0.5256</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K. FARIED</t>
+          <t>J. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.0918</v>
+        <v>4.1331</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9703</v>
+        <v>-0.1375</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1215</v>
+        <v>4.2705</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0122</v>
+        <v>2.4251</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9923999999999999</v>
+        <v>0.742</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9802999999999999</v>
+        <v>1.6831</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1548</v>
+        <v>0.2988</v>
       </c>
       <c r="K5" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.9747</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0736</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1426</v>
+        <v>2.1263</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9113</v>
+        <v>-0.2327</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0539</v>
+        <v>2.359</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="S5" t="n">
-        <v>1.8477</v>
+        <v>0.0844</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9752</v>
+        <v>-0.4362</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8725000000000001</v>
+        <v>0.5206</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.0535</v>
+        <v>3.9527</v>
       </c>
       <c r="E6" t="n">
         <v>0.5701000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>3.4834</v>
+        <v>3.3826</v>
       </c>
       <c r="G6" t="n">
         <v>2.2163</v>
@@ -922,13 +922,13 @@
         <v>1.8556</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4635</v>
+        <v>0.3626</v>
       </c>
       <c r="T6" t="n">
         <v>-0.0351</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4986</v>
+        <v>0.3978</v>
       </c>
       <c r="V6" t="n">
         <v>0.6778999999999999</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.7271</v>
+        <v>3.7436</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7361</v>
+        <v>1.6182</v>
       </c>
       <c r="F7" t="n">
-        <v>1.991</v>
+        <v>2.1254</v>
       </c>
       <c r="G7" t="n">
         <v>4.8619</v>
@@ -1000,13 +1000,13 @@
         <v>2.0876</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2249</v>
+        <v>-0.2084</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1098</v>
+        <v>-0.2278</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1151</v>
+        <v>0.0193</v>
       </c>
       <c r="V7" t="n">
         <v>-0.6778999999999999</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. SLOUKAS</t>
+          <t>K. FARIED</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,40 +1033,40 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>3.4835</v>
+        <v>3.166</v>
       </c>
       <c r="E8" t="n">
-        <v>1.0507</v>
+        <v>1.3805</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4328</v>
+        <v>1.7855</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6309</v>
+        <v>0.0122</v>
       </c>
       <c r="H8" t="n">
-        <v>3.27</v>
+        <v>0.9923999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6391</v>
+        <v>-0.9802999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>1.8801</v>
+        <v>0.1548</v>
       </c>
       <c r="K8" t="n">
-        <v>2.2015</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.3213</v>
+        <v>0.0736</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7507</v>
+        <v>-0.1426</v>
       </c>
       <c r="N8" t="n">
-        <v>1.0685</v>
+        <v>0.9113</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3178</v>
+        <v>-1.0539</v>
       </c>
       <c r="P8" t="n">
         <v>1.1598</v>
@@ -1078,19 +1078,19 @@
         <v>1.3917</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3071</v>
+        <v>0.9219000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5975</v>
+        <v>0.3855</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2904</v>
+        <v>0.5364</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. GRANT</t>
+          <t>N. HAYES-DAVIS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3648</v>
+        <v>1.8602</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5177</v>
+        <v>0.7203000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>2.8826</v>
+        <v>1.1399</v>
       </c>
       <c r="G9" t="n">
-        <v>1.9047</v>
+        <v>0.5766</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7286</v>
+        <v>1.3362</v>
       </c>
       <c r="I9" t="n">
-        <v>2.6334</v>
+        <v>-0.7596000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2395</v>
+        <v>0.6768999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3494</v>
+        <v>0.9614</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5889</v>
+        <v>-0.2845</v>
       </c>
       <c r="M9" t="n">
-        <v>1.6653</v>
+        <v>-0.1003</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3792</v>
+        <v>0.3748</v>
       </c>
       <c r="O9" t="n">
-        <v>2.0445</v>
+        <v>-0.4751</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.3917</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1598</v>
+        <v>-0.232</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5399</v>
+        <v>-0.1081</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5975</v>
+        <v>0.2754</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0576</v>
+        <v>-0.3835</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N. HAYES-DAVIS</t>
+          <t>T. SHORTS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,40 +1189,40 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2882</v>
+        <v>1.723</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4844</v>
+        <v>0.4579</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8038</v>
+        <v>1.2651</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5766</v>
+        <v>0.4139</v>
       </c>
       <c r="H10" t="n">
-        <v>1.3362</v>
+        <v>0.9157</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7596000000000001</v>
+        <v>-0.5018</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6768999999999999</v>
+        <v>0.5677</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9614</v>
+        <v>0.3837</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.2845</v>
+        <v>0.184</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1003</v>
+        <v>-0.1538</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3748</v>
+        <v>0.5321</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4751</v>
+        <v>-0.6859</v>
       </c>
       <c r="P10" t="n">
         <v>1.3917</v>
@@ -1234,13 +1234,13 @@
         <v>1.6237</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.68</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0395</v>
+        <v>0.1221</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7196</v>
+        <v>-0.2047</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T. SHORTS</t>
+          <t>J. GRANT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9137999999999999</v>
+        <v>1.5164</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.4858</v>
+        <v>-1.3998</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3996</v>
+        <v>2.9162</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4139</v>
+        <v>1.9047</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9157</v>
+        <v>-0.7286</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5018</v>
+        <v>2.6334</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5677</v>
+        <v>0.2395</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3837</v>
+        <v>-0.3494</v>
       </c>
       <c r="L11" t="n">
-        <v>0.184</v>
+        <v>0.5889</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1538</v>
+        <v>1.6653</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5321</v>
+        <v>-0.3792</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6859</v>
+        <v>2.0445</v>
       </c>
       <c r="P11" t="n">
-        <v>1.3917</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.232</v>
+        <v>-1.1598</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8918</v>
+        <v>-0.3883</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8215</v>
+        <v>-0.4795</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0703</v>
+        <v>0.0912</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>K. MITOGLOU</t>
+          <t>P. KALAITZAKIS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,37 +1345,37 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0688</v>
+        <v>-0.2982</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.4065</v>
+        <v>1.0598</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3377</v>
+        <v>-1.3581</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.1343</v>
+        <v>0.544</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.0001</v>
+        <v>0.8919</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.1343</v>
+        <v>-0.348</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.6804</v>
+        <v>1.1659</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.9677</v>
+        <v>1.0923</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.7127</v>
+        <v>0.0736</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.4539</v>
+        <v>-0.622</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0323</v>
+        <v>-0.2004</v>
       </c>
       <c r="O12" t="n">
         <v>-0.4216</v>
@@ -1390,28 +1390,28 @@
         <v>0.6959</v>
       </c>
       <c r="S12" t="n">
-        <v>1.3697</v>
+        <v>-0.4659</v>
       </c>
       <c r="T12" t="n">
-        <v>1.274</v>
+        <v>-0.1061</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0958</v>
+        <v>-0.3598</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. KALAITZAKIS</t>
+          <t>K. MITOGLOU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,37 +1423,37 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.4834</v>
+        <v>-1.2812</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9419</v>
+        <v>-1.3501</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.4253</v>
+        <v>0.0689</v>
       </c>
       <c r="G13" t="n">
-        <v>0.544</v>
+        <v>-2.1343</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8919</v>
+        <v>-1.0001</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.348</v>
+        <v>-1.1343</v>
       </c>
       <c r="J13" t="n">
-        <v>1.1659</v>
+        <v>-1.6804</v>
       </c>
       <c r="K13" t="n">
-        <v>1.0923</v>
+        <v>-0.9677</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0736</v>
+        <v>-0.7127</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.622</v>
+        <v>-0.4539</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2004</v>
+        <v>-0.0323</v>
       </c>
       <c r="O13" t="n">
         <v>-0.4216</v>
@@ -1468,22 +1468,22 @@
         <v>0.6959</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.651</v>
+        <v>0.1573</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.224</v>
+        <v>0.3304</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.427</v>
+        <v>-0.1731</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>35.0207</v>
+        <v>35.0211</v>
       </c>
       <c r="E14" t="n">
-        <v>15.583</v>
+        <v>15.5831</v>
       </c>
       <c r="F14" t="n">
         <v>19.4378</v>
@@ -1522,13 +1522,13 @@
         <v>16.3393</v>
       </c>
       <c r="K14" t="n">
-        <v>9.480699999999997</v>
+        <v>9.480699999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>6.858700000000001</v>
+        <v>6.8587</v>
       </c>
       <c r="M14" t="n">
-        <v>7.181899999999998</v>
+        <v>7.1819</v>
       </c>
       <c r="N14" t="n">
         <v>0.6566</v>
@@ -1540,19 +1540,19 @@
         <v>10.438</v>
       </c>
       <c r="Q14" t="n">
-        <v>-6.958900000000001</v>
+        <v>-6.9589</v>
       </c>
       <c r="R14" t="n">
         <v>17.3967</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6677999999999995</v>
+        <v>0.6678000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>0.02189999999999978</v>
+        <v>0.02200000000000013</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6459000000000001</v>
+        <v>0.6458999999999996</v>
       </c>
       <c r="V14" t="n">
         <v>0.3942999999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.032</v>
+        <v>-0.2484</v>
       </c>
       <c r="E15" t="n">
-        <v>2.792</v>
+        <v>1.6125</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.7601</v>
+        <v>-1.8609</v>
       </c>
       <c r="G15" t="n">
         <v>0.3774</v>
@@ -1624,13 +1624,13 @@
         <v>0.4639</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5643</v>
+        <v>0.284</v>
       </c>
       <c r="T15" t="n">
-        <v>1.6122</v>
+        <v>0.4327</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0479</v>
+        <v>-0.1487</v>
       </c>
       <c r="V15" t="n">
         <v>-0.6778999999999999</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>V. POIRIER</t>
+          <t>C. SWIDER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.318</v>
+        <v>-1.7159</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2023</v>
+        <v>-2.0433</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8843</v>
+        <v>0.3274</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.5556</v>
+        <v>-2.3116</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.0638</v>
+        <v>-0.5114</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4918</v>
+        <v>-1.8002</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.4366</v>
+        <v>-1.5324</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.4734</v>
+        <v>0.0035</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0368</v>
+        <v>-1.5359</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.119</v>
+        <v>-0.7792</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5904</v>
+        <v>-0.5149</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5286</v>
+        <v>-0.2643</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.5515</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="S16" t="n">
-        <v>3.4973</v>
+        <v>-0.1002</v>
       </c>
       <c r="T16" t="n">
-        <v>3.1181</v>
+        <v>-0.5109</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3791</v>
+        <v>0.4107</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. SWIDER</t>
+          <t>S. HAZER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.7502</v>
+        <v>-1.9466</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.2792</v>
+        <v>0.3828</v>
       </c>
       <c r="F17" t="n">
-        <v>0.529</v>
+        <v>-2.3295</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.3116</v>
+        <v>-2.3255</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5114</v>
+        <v>-1.0708</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.8002</v>
+        <v>-1.2548</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.5324</v>
+        <v>0.0018</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0035</v>
+        <v>0.3599</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.5359</v>
+        <v>-0.3581</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7792</v>
+        <v>-2.3273</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5149</v>
+        <v>-1.4306</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2643</v>
+        <v>-0.8966</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6959</v>
+        <v>-2.5515</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.5515</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1344</v>
+        <v>0.1081</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7468</v>
+        <v>0.1103</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6124000000000001</v>
+        <v>-0.0022</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>2.8223</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.8223</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. BEAUBOIS</t>
+          <t>V. POIRIER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.9099</v>
+        <v>-2.0911</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.5394</v>
+        <v>-1.0388</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3705</v>
+        <v>-1.0523</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.871</v>
+        <v>-1.5556</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.8006</v>
+        <v>-1.0638</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0703</v>
+        <v>-0.4918</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0378</v>
+        <v>-0.4366</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2318</v>
+        <v>-0.4734</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1939</v>
+        <v>0.0368</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8331</v>
+        <v>-1.119</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5688</v>
+        <v>-0.5904</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2643</v>
+        <v>-0.5286</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.6959</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.3917</v>
+        <v>-2.5515</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3431</v>
+        <v>1.0881</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1098</v>
+        <v>0.8771</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2333</v>
+        <v>0.2111</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. HAZER</t>
+          <t>R. BEAUBOIS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.4527</v>
+        <v>-2.2302</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3249</v>
+        <v>-1.8932</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.1278</v>
+        <v>-0.3369</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.3255</v>
+        <v>-0.871</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.0708</v>
+        <v>-0.8006</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.2548</v>
+        <v>-0.0703</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0018</v>
+        <v>-0.0378</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3599</v>
+        <v>-0.2318</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.3581</v>
+        <v>0.1939</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.3273</v>
+        <v>-0.8331</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.4306</v>
+        <v>-0.5688</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8966</v>
+        <v>-0.2643</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.5515</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.5515</v>
+        <v>-1.3917</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>0.6959</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.398</v>
+        <v>-0.6633</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5975</v>
+        <v>-0.4637</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1994</v>
+        <v>-0.1997</v>
       </c>
       <c r="V19" t="n">
-        <v>2.8223</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.8223</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. YILMAZ</t>
+          <t>S. LEE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7226</v>
+        <v>-2.4348</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2397</v>
+        <v>-2.7087</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4829</v>
+        <v>0.2739</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.1213</v>
+        <v>-3.0923</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0707</v>
+        <v>-1.3457</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0506</v>
+        <v>-1.7467</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4671</v>
+        <v>-2.8061</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3193</v>
+        <v>-1.2702</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.7863</v>
+        <v>-1.5359</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6543</v>
+        <v>-0.2862</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.39</v>
+        <v>-0.0755</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2643</v>
+        <v>-0.2108</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.3917</v>
+        <v>0.232</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.6237</v>
+        <v>-0.4639</v>
       </c>
       <c r="R20" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2095</v>
+        <v>-0.6467000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2908</v>
+        <v>-0.5109</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0813</v>
+        <v>-0.1357</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. LEE</t>
+          <t>E. YILMAZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8724</v>
+        <v>-2.4531</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.9446</v>
+        <v>-2.0038</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0722</v>
+        <v>-0.4492</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.0923</v>
+        <v>-1.1213</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.3457</v>
+        <v>-0.0707</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.7467</v>
+        <v>-1.0506</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.8061</v>
+        <v>-0.4671</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.2702</v>
+        <v>0.3193</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.5359</v>
+        <v>-0.7863</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2862</v>
+        <v>-0.6543</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0755</v>
+        <v>-0.39</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2108</v>
+        <v>-0.2643</v>
       </c>
       <c r="P21" t="n">
+        <v>-1.3917</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-1.6237</v>
+      </c>
+      <c r="R21" t="n">
         <v>0.232</v>
       </c>
-      <c r="Q21" t="n">
-        <v>-0.4639</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0.6959</v>
-      </c>
       <c r="S21" t="n">
-        <v>-1.0842</v>
+        <v>0.06</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7468</v>
+        <v>-0.0549</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3374</v>
+        <v>0.1149</v>
       </c>
       <c r="V21" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.3837</v>
+        <v>-3.6088</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0696</v>
+        <v>-0.3619</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.3141</v>
+        <v>-3.2469</v>
       </c>
       <c r="G22" t="n">
         <v>-1.1862</v>
@@ -2170,13 +2170,13 @@
         <v>0.232</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9656</v>
+        <v>-0.1907</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5975</v>
+        <v>0.1103</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3681</v>
+        <v>-0.3009</v>
       </c>
       <c r="V22" t="n">
         <v>-1.0722</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. LOYD</t>
+          <t>B. DESSERT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.4456</v>
+        <v>-3.9404</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.4125</v>
+        <v>-1.3819</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.0332</v>
+        <v>-2.5585</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.797</v>
+        <v>-2.9022</v>
       </c>
       <c r="H23" t="n">
-        <v>1.054</v>
+        <v>-2.0959</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.8509</v>
+        <v>-0.8063</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5918</v>
+        <v>-0.6823</v>
       </c>
       <c r="K23" t="n">
-        <v>1.5733</v>
+        <v>-0.7191</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.1651</v>
+        <v>0.0368</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.2052</v>
+        <v>-2.2199</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5194</v>
+        <v>-1.3767</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6859</v>
+        <v>-0.8431</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.2473</v>
+        <v>-0.232</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4709</v>
+        <v>-0.5021</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2513</v>
+        <v>-0.4676</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2196</v>
+        <v>-0.0345</v>
       </c>
       <c r="V23" t="n">
-        <v>0.1418</v>
+        <v>-0.5361</v>
       </c>
       <c r="W23" t="n">
-        <v>0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>-0.5361</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B. DESSERT</t>
+          <t>N. WEILER-BABB</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.4623</v>
+        <v>-3.9575</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.7358</v>
+        <v>-3.1028</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.7265</v>
+        <v>-0.8548</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.9022</v>
+        <v>-2.2072</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.0959</v>
+        <v>-0.7718</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.8063</v>
+        <v>-1.4354</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6823</v>
+        <v>-0.5948</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.7191</v>
+        <v>0.1547</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0368</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.2199</v>
+        <v>-1.6123</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.3767</v>
+        <v>-0.9265</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.8431</v>
+        <v>-0.6859</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.232</v>
+        <v>-2.5515</v>
       </c>
       <c r="R24" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.024</v>
+        <v>0.1052</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8215</v>
+        <v>0.0435</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2025</v>
+        <v>0.0617</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>N. WEILER-BABB</t>
+          <t>J. LOYD</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.6316</v>
+        <v>-4.0081</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.8105</v>
+        <v>-3.1766</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.8212</v>
+        <v>-0.8315</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.2072</v>
+        <v>-1.797</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.7718</v>
+        <v>1.054</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.4354</v>
+        <v>-2.8509</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.5948</v>
+        <v>-0.5918</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1547</v>
+        <v>1.5733</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.7495000000000001</v>
+        <v>-2.1651</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.6123</v>
+        <v>-1.2052</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.9265</v>
+        <v>-0.5194</v>
       </c>
       <c r="O25" t="n">
         <v>-0.6859</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.8556</v>
+        <v>-2.3195</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.5515</v>
+        <v>-3.2473</v>
       </c>
       <c r="R25" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5689</v>
+        <v>-0.0334</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6642</v>
+        <v>-0.0154</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0953</v>
+        <v>-0.018</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="26">
@@ -2437,10 +2437,10 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.7399</v>
+        <v>-6.386</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.076</v>
+        <v>-3.7221</v>
       </c>
       <c r="F26" t="n">
         <v>-2.6639</v>
@@ -2482,10 +2482,10 @@
         <v>1.1598</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.5306999999999999</v>
+        <v>-0.1768</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.55</v>
+        <v>-0.1962</v>
       </c>
       <c r="U26" t="n">
         <v>0.0193</v>
@@ -2518,10 +2518,10 @@
         <v>-35.0209</v>
       </c>
       <c r="E27" t="n">
-        <v>-19.4379</v>
+        <v>-19.4378</v>
       </c>
       <c r="F27" t="n">
-        <v>-15.5833</v>
+        <v>-15.5831</v>
       </c>
       <c r="G27" t="n">
         <v>-23.5212</v>
@@ -2536,7 +2536,7 @@
         <v>-7.181999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.6565</v>
+        <v>-0.6565000000000002</v>
       </c>
       <c r="L27" t="n">
         <v>-6.525700000000001</v>
@@ -2545,10 +2545,10 @@
         <v>-16.339</v>
       </c>
       <c r="N27" t="n">
-        <v>-9.480400000000001</v>
+        <v>-9.480399999999999</v>
       </c>
       <c r="O27" t="n">
-        <v>-6.8587</v>
+        <v>-6.858700000000001</v>
       </c>
       <c r="P27" t="n">
         <v>-10.4379</v>
@@ -2557,16 +2557,16 @@
         <v>-17.3966</v>
       </c>
       <c r="R27" t="n">
-        <v>6.9589</v>
+        <v>6.958899999999999</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.6676999999999997</v>
+        <v>-0.6677999999999999</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.6459000000000008</v>
+        <v>-0.6457000000000002</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.02199999999999997</v>
+        <v>-0.02199999999999999</v>
       </c>
       <c r="V27" t="n">
         <v>-0.3943000000000001</v>
